--- a/data/raw/Image.xlsx
+++ b/data/raw/Image.xlsx
@@ -377,7 +377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.42578125" defaultRowHeight="19"/>
   <cols>
     <col width="5.5703125" customWidth="1" style="8" min="1" max="1"/>
@@ -7689,6 +7689,66 @@
       <c r="O104" s="13" t="inlineStr">
         <is>
           <t>image_alternative</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>I_104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>IMG_teaparty_tenniel.svg</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Public Domain</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Public Domain</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>John Tenniel</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Mad Tea Party scene by Tenniel from the 1865 first edition</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ST_001</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>CH_001, CH_004, CH_007, CH_018</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>104</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Noémi Villars-Amberg, Daniela Subotic</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>image</t>
         </is>
       </c>
     </row>
